--- a/public/templates/Item_sample_template.xlsx
+++ b/public/templates/Item_sample_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="141">
   <si>
     <t>S.No</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>Sell Price Currency</t>
+  </si>
+  <si>
+    <t>Mrp</t>
+  </si>
+  <si>
+    <t>Mrp Currency</t>
   </si>
   <si>
     <t>Min Stocking Level</t>
@@ -1180,7 +1186,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1725,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:DX3"/>
+  <dimension ref="A1:DZ3"/>
   <sheetFormatPr defaultColWidth="8.71296296296296" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="9.57407407407407" customWidth="1"/>
@@ -1736,24 +1742,24 @@
     <col min="6" max="7" width="15.287037037037" customWidth="1"/>
     <col min="8" max="8" width="16.712962962963" customWidth="1"/>
     <col min="9" max="9" width="12.5740740740741" customWidth="1"/>
-    <col min="20" max="20" width="11.2222222222222" customWidth="1"/>
-    <col min="21" max="21" width="11.7777777777778" customWidth="1"/>
-    <col min="22" max="22" width="10.4444444444444" customWidth="1"/>
-    <col min="23" max="23" width="11.2222222222222" customWidth="1"/>
+    <col min="22" max="22" width="11.2222222222222" customWidth="1"/>
+    <col min="23" max="23" width="11.7777777777778" customWidth="1"/>
     <col min="24" max="24" width="10.4444444444444" customWidth="1"/>
-    <col min="25" max="25" width="10.3333333333333" customWidth="1"/>
-    <col min="27" max="27" width="11.3333333333333" customWidth="1"/>
-    <col min="28" max="28" width="9.88888888888889" customWidth="1"/>
-    <col min="30" max="30" width="12.1111111111111" customWidth="1"/>
-    <col min="31" max="31" width="12.7777777777778" customWidth="1"/>
-    <col min="34" max="34" width="10.2222222222222" customWidth="1"/>
-    <col min="35" max="36" width="9.77777777777778" customWidth="1"/>
-    <col min="62" max="62" width="21" customWidth="1"/>
-    <col min="63" max="63" width="17" customWidth="1"/>
-    <col min="66" max="66" width="9.11111111111111" customWidth="1"/>
+    <col min="25" max="25" width="11.2222222222222" customWidth="1"/>
+    <col min="26" max="26" width="10.4444444444444" customWidth="1"/>
+    <col min="27" max="27" width="10.3333333333333" customWidth="1"/>
+    <col min="29" max="29" width="11.3333333333333" customWidth="1"/>
+    <col min="30" max="30" width="9.88888888888889" customWidth="1"/>
+    <col min="32" max="32" width="12.1111111111111" customWidth="1"/>
+    <col min="33" max="33" width="12.7777777777778" customWidth="1"/>
+    <col min="36" max="36" width="10.2222222222222" customWidth="1"/>
+    <col min="37" max="38" width="9.77777777777778" customWidth="1"/>
+    <col min="64" max="64" width="21" customWidth="1"/>
+    <col min="65" max="65" width="17" customWidth="1"/>
+    <col min="68" max="68" width="9.11111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:118">
+    <row r="1" s="1" customFormat="1" ht="99" customHeight="1" spans="1:120">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2090,87 +2096,91 @@
       <c r="DH1" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="DI1" s="3"/>
-      <c r="DJ1" s="3"/>
+      <c r="DI1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="DK1" s="3"/>
       <c r="DL1" s="3"/>
       <c r="DM1" s="3"/>
       <c r="DN1" s="3"/>
+      <c r="DO1" s="3"/>
+      <c r="DP1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="183" customHeight="1" spans="2:128">
+    <row r="2" s="2" customFormat="1" ht="183" customHeight="1" spans="2:130">
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>123</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>127</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BP2" s="8"/>
-      <c r="BT2" s="8"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
+        <v>128</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BR2" s="8"/>
+      <c r="BV2" s="8"/>
       <c r="DK2"/>
       <c r="DL2"/>
       <c r="DM2"/>
       <c r="DN2"/>
-      <c r="DO2" s="3"/>
-      <c r="DP2" s="3"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
       <c r="DQ2" s="3"/>
       <c r="DR2" s="3"/>
       <c r="DS2" s="3"/>
@@ -2178,34 +2188,30 @@
       <c r="DU2" s="3"/>
       <c r="DV2" s="3"/>
       <c r="DW2" s="3"/>
-      <c r="DX2"/>
+      <c r="DX2" s="3"/>
+      <c r="DY2" s="3"/>
+      <c r="DZ2"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:128">
+    <row r="3" s="3" customFormat="1" ht="22" customHeight="1" spans="1:130">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G3" s="3">
         <v>94042910</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BJ3" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="BK3" s="3" t="s">
         <v>134</v>
       </c>
       <c r="BL3" s="3" t="s">
@@ -2220,8 +2226,12 @@
       <c r="BO3" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="DI3"/>
-      <c r="DJ3"/>
+      <c r="BP3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="BQ3" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="DK3"/>
       <c r="DL3"/>
       <c r="DM3"/>
@@ -2236,6 +2246,8 @@
       <c r="DV3"/>
       <c r="DW3"/>
       <c r="DX3"/>
+      <c r="DY3"/>
+      <c r="DZ3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:F2">
